--- a/doc/AbCS_Version3_Release_Tester_Review.xlsx
+++ b/doc/AbCS_Version3_Release_Tester_Review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Version 3 Plans" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Version 3 Plans'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Version 3 Plans'!$A$1:$K$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1819,17 +1819,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Follow-on - Post-v3</t>
+          <t>Follow-on</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Better plot search</t>
+          <t>View-mode field announcements</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Faster search inside long plot summaries on very large libraries.</t>
+          <t>In Book Details view mode, tabbing a field should speak the name and value without JAWS saying edit or read only. Edit mode stays a real edit field.</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>3-5 days</t>
+          <t>2-4 days</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Full-text index sync and rebuild add complexity.</t>
+          <t>Must keep real edit widgets in edit mode; a prior attempt that cleared read-only made JAWS say edit.</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Post-v3; most useful on very large libraries</t>
+          <t>Anytime / accessibility</t>
         </is>
       </c>
     </row>
@@ -1949,22 +1949,22 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Follow-on</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Import from other apps</t>
+          <t>Import tag mapping</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Import a library export from another tool (for example Libib or similar CSV formats) with less manual editing.</t>
+          <t>In Preferences Import Settings, choose which audio tags fill book title and author (album vs track title, album artist vs artist). Files still group by album so a multi-part book stays one book. Series from the file name stays an import scenario.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
@@ -1972,29 +1972,29 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>1-2 weeks per format</t>
+          <t>2-3 days</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Third-party export formats change; ongoing maintenance per adapter.</t>
+          <t>Wrong default would change existing imports; grouping must stay on album, not track title.</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Demand-driven after core waves</t>
+          <t>Anytime / import</t>
         </is>
       </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Saved smart lists</t>
+          <t>Import from other apps</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Save a combination of filters (for example unread sci-fi with a plot) and reuse it with one click.</t>
+          <t>Import a library export from another tool (for example Libib or similar CSV formats) with less manual editing.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -2017,29 +2017,29 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>1-2 weeks</t>
+          <t>1-2 weeks per format</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Users may confuse saved smart lists with normal collections.</t>
+          <t>Third-party export formats change; ongoing maintenance per adapter.</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>After core filter features land</t>
+          <t>Demand-driven after core waves</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Reading progress</t>
+          <t>Saved smart lists</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Remember how far you got in a book (not just finished or not). Mainly useful if deeper playback support is added later. Not an in-app player.</t>
+          <t>Save a combination of filters (for example unread sci-fi with a plot) and reuse it with one click.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
@@ -2062,29 +2062,29 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2-3 weeks+</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Conflicts with AbCS focus as a collection manager rather than a player.</t>
+          <t>Users may confuse saved smart lists with normal collections.</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Demand-driven; deferred unless strong tester demand</t>
+          <t>After core filter features land</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Tags on books</t>
+          <t>Reading progress</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Multiple labels per book (for example gift or book club) without changing its collection.</t>
+          <t>Remember how far you got in a book (not just finished or not). Mainly useful if deeper playback support is added later. Not an in-app player.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
@@ -2107,29 +2107,29 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>2-3 weeks</t>
+          <t>2-3 weeks+</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Overlaps conceptually with Want to Read and collections; needs clear guidance.</t>
+          <t>Conflicts with AbCS focus as a collection manager rather than a player.</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Demand-driven backlog</t>
+          <t>Demand-driven; deferred unless strong tester demand</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Check for updates</t>
+          <t>Tags on books</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Help menu option to see if a newer AbCS version is available and open the download page. No silent install.</t>
+          <t>Multiple labels per book (for example gift or book club) without changing its collection.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -2152,44 +2152,44 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2-3 days</t>
+          <t>2-3 weeks</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Offline users see nothing; no telemetry in v1.</t>
+          <t>Overlaps conceptually with Want to Read and collections; needs clear guidance.</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Anytime; good small release win</t>
+          <t>Demand-driven backlog</t>
         </is>
       </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Maintenance - not user-facing</t>
+          <t>Backlog</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>CI / test hardening</t>
+          <t>Check for updates</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Strengthen automated regression testing for version 3 waves. Supports safer development. Not a user-visible feature.</t>
+          <t>Help menu option to see if a newer AbCS version is available and open the download page. No silent install.</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>1-2 days setup + ongoing</t>
+          <t>2-3 days</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2207,19 +2207,19 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure work; does not change app features for end users.</t>
+          <t>Offline users see nothing; no telemetry in v1.</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Between waves; early in the version 3 cycle</t>
+          <t>Anytime; good small release win</t>
         </is>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>M01</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Dead-code cleanup</t>
+          <t>CI / test hardening</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Periodic cleanup of unused code to keep the project easier to maintain. Not a user-visible feature.</t>
+          <t>Strengthen automated regression testing for version 3 waves. Supports safer development. Not a user-visible feature.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
@@ -2242,27 +2242,72 @@
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr">
         <is>
+          <t>1-2 days setup + ongoing</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure work; does not change app features for end users.</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Between waves; early in the version 3 cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance - not user-facing</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Dead-code cleanup</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Periodic cleanup of unused code to keep the project easier to maintain. Not a user-visible feature.</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>0.5-1 day per pass</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Only removes confirmed unused code after tests pass.</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Between waves or before release tags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K35"/>
+  <autoFilter ref="A1:K36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/doc/AbCS_Version3_Release_Tester_Review.xlsx
+++ b/doc/AbCS_Version3_Release_Tester_Review.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="247">
   <si>
     <t xml:space="preserve">AbCS Version 3 Release Tester Review</t>
   </si>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Run web metadata fetch on a background thread so the app stays responsive during network calls. Cancel still works. Progress announcements stay on the GUI thread.</t>
   </si>
   <si>
-    <t xml:space="preserve">X</t>
+    <t xml:space="preserve">out of scope for v3</t>
   </si>
   <si>
     <t xml:space="preserve">v3</t>
@@ -176,6 +176,9 @@
     <t xml:space="preserve">Queue web metadata fetch for a selection of books with progress and cancel - instead of one book at a time. Per-book review remains recommended.</t>
   </si>
   <si>
+    <t xml:space="preserve">v3 </t>
+  </si>
+  <si>
     <t xml:space="preserve">1-2 weeks</t>
   </si>
   <si>
@@ -215,6 +218,9 @@
     <t xml:space="preserve">In Book Details view mode, tabbing a field should speak the name and value without JAWS saying edit or read only. Edit mode stays a real edit field.</t>
   </si>
   <si>
+    <t xml:space="preserve">v3 pending </t>
+  </si>
+  <si>
     <t xml:space="preserve">2-4 days</t>
   </si>
   <si>
@@ -278,6 +284,9 @@
     <t xml:space="preserve">Behind-the-scenes database upgrade that adds storage for Want to Read, ratings, cover images, and collection folder paths. You will not see new buttons yet, but import, backup, and older databases should still work.</t>
   </si>
   <si>
+    <t xml:space="preserve">V3 modifyed </t>
+  </si>
+  <si>
     <t xml:space="preserve">Touches the database all features use; must not break import or legacy backup/restore.</t>
   </si>
   <si>
@@ -390,6 +399,9 @@
   </si>
   <si>
     <t xml:space="preserve">Optional folder path for each collection (for example where your Audible rips live). Import and rescan default to that folder. No files are moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V3 </t>
   </si>
   <si>
     <t xml:space="preserve">Optional path on collections; import pre-fill only.</t>
@@ -856,28 +868,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1155,149 +1171,149 @@
   <dimension ref="A1:A31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
+      <c r="A12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
+      <c r="A28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1320,1101 +1336,1111 @@
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="I32" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="J32" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="I34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="K35" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="K36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>242</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
